--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.70578732604821</v>
+        <v>7.589690440482834</v>
       </c>
       <c r="D2" t="n">
-        <v>46.7233913583475</v>
+        <v>7.592551095731468</v>
       </c>
       <c r="E2" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F2" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.02142540915647</v>
+        <v>6.015981628987927</v>
       </c>
       <c r="D3" t="n">
-        <v>37.02315762550137</v>
+        <v>6.016263114143973</v>
       </c>
       <c r="E3" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F3" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.75272382792357</v>
+        <v>6.134817622037581</v>
       </c>
       <c r="D4" t="n">
-        <v>37.78537671184732</v>
+        <v>6.140123715675189</v>
       </c>
       <c r="E4" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F4" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.41397287763207</v>
+        <v>8.679770592615212</v>
       </c>
       <c r="D5" t="n">
-        <v>53.33999554181873</v>
+        <v>8.667749275545544</v>
       </c>
       <c r="E5" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F5" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.7466049725614</v>
+        <v>11.00882330804123</v>
       </c>
       <c r="D6" t="n">
-        <v>67.66536892730014</v>
+        <v>10.99562245068627</v>
       </c>
       <c r="E6" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F6" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.66767706298862</v>
+        <v>9.208497522735652</v>
       </c>
       <c r="D7" t="n">
-        <v>56.58691547493186</v>
+        <v>9.195373764676427</v>
       </c>
       <c r="E7" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F7" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.03298830624071</v>
+        <v>2.605360599764115</v>
       </c>
       <c r="D8" t="n">
-        <v>16.11988826732254</v>
+        <v>2.619481843439913</v>
       </c>
       <c r="E8" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F8" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.11199209720157</v>
+        <v>6.843198715795256</v>
       </c>
       <c r="D9" t="n">
-        <v>42.0227811590518</v>
+        <v>6.828701938345918</v>
       </c>
       <c r="E9" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F9" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.50786900539764</v>
+        <v>3.170028713377116</v>
       </c>
       <c r="D10" t="n">
-        <v>19.53501993435566</v>
+        <v>3.174440739332795</v>
       </c>
       <c r="E10" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F10" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.16053153543255</v>
+        <v>4.413586374507789</v>
       </c>
       <c r="D11" t="n">
-        <v>40.72584741067052</v>
+        <v>6.617950204233959</v>
       </c>
       <c r="E11" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F11" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.97391473549592</v>
+        <v>2.920761144518087</v>
       </c>
       <c r="D12" t="n">
-        <v>43.03387727703448</v>
+        <v>6.993005057518104</v>
       </c>
       <c r="E12" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F12" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.031062545622627</v>
+        <v>1.467547663663677</v>
       </c>
       <c r="D13" t="n">
-        <v>45.13199465637236</v>
+        <v>7.333949131660508</v>
       </c>
       <c r="E13" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F13" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.412043250918815</v>
+        <v>1.366957028274308</v>
       </c>
       <c r="D14" t="n">
-        <v>44.11785772189937</v>
+        <v>7.169151879808648</v>
       </c>
       <c r="E14" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F14" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.290778546165575</v>
+        <v>1.509751513751906</v>
       </c>
       <c r="D15" t="n">
-        <v>29.96188850021188</v>
+        <v>4.868806881284431</v>
       </c>
       <c r="E15" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F15" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.45690496706232</v>
+        <v>2.836747057147627</v>
       </c>
       <c r="D16" t="n">
-        <v>17.3479951126408</v>
+        <v>2.819049205804129</v>
       </c>
       <c r="E16" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F16" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.467010168607211</v>
+        <v>0.8883891523986718</v>
       </c>
       <c r="D17" t="n">
-        <v>36.16594339846171</v>
+        <v>5.876965802250028</v>
       </c>
       <c r="E17" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F17" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.294965503571857</v>
+        <v>0.8604318943304269</v>
       </c>
       <c r="D18" t="n">
-        <v>5.185691464662222</v>
+        <v>0.8426748630076111</v>
       </c>
       <c r="E18" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F18" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>11.88766221254884</v>
+        <v>1.931745109539186</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61385597170866</v>
+        <v>8.874751595402657</v>
       </c>
       <c r="E19" t="n">
-        <v>19.0970659377754</v>
+        <v>3.103273214888503</v>
       </c>
       <c r="F19" t="n">
-        <v>15.52337696282614</v>
+        <v>2.522548756459249</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
